--- a/data/trans_bre/IQ09_D_R3-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IQ09_D_R3-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -522,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que llevan más tiempo (cuartil más desfavorable) sufriendo esa dolencia, enfermedad o impedimento que le haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Menores que llevan más tiempo (cuartil más desfavorable: más de 2161 días) sufriendo esa dolencia, enfermedad o impedimento que le haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -610,299 +619,159 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>13,57</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,28</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>69,77%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>36,51%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>13.56924590600955</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.277268834234415</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.6977154040171071</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.3651164770141854</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-45,63; 80,64</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-18,57; 40,91</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-45.6307178901505</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-18.57194044163021</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>80.64032592223781</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>40.91042261422055</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-15,04</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-7,25</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,29</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-10,36</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-49,44%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-25,73%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-28,7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-35,67; -4,79</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-22,14; 8,76</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-18,3; 15,21</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-39,35; 24,16</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-82,82; 150,4</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-15.04019901731086</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-7.253582359146193</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-2.285403957323129</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-10.36406207728769</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.4943567103015029</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.2573360827817242</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.2869568499630366</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-6,5</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-15,63</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-13,31</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,12</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-22,81%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-35.67300783820329</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-22.14076269880724</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-18.298862133966</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-39.34903193583514</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="n">
+        <v>-0.8282474300472901</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-56,38; 52,34</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-65,82; 0,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-54,4; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-48,22; 54,58</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-4.786955519822059</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>8.758701950050831</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>15.20952668380794</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>24.16129319795316</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="n">
+        <v>1.504027454170082</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +779,177 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-8,72</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-6,18</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-4,81</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,84</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-46,88%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-45,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-51,2%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-9,77%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-6.501156834850375</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-15.62921458696644</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-13.31326665195295</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.115549599119542</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2280649955660871</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.0324116574147028</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-27,8; 12,24</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-17,59; 7,67</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-17,39; 9,24</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-27,0; 20,78</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 222,76</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 125,79</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-73,56; 140,5</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-56.37537383945978</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-65.81921097650508</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-54.40479182180644</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-48.21686066210881</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>52.33935594630563</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>54.58465503688098</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-8.717846516673578</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-6.180163843580814</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-4.810294592019301</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2.835173449622475</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.4688212380081302</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.4530603166831068</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.5120406506063031</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.09765414716386604</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-27.8022477075037</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-17.59463268895477</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-17.38626169391643</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-27.00370152054597</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="n">
+        <v>-0.7355869064404832</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>12.23666031974166</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7.673652574205038</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>9.23960880562823</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>20.77990272510416</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>2.227600279015077</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.257855993518094</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="n">
+        <v>1.405014090350534</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +957,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
